--- a/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y49"/>
+  <dimension ref="A1:Y50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2430,7 +2430,7 @@
         <v>1621</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>442.09</v>
+        <v>530.51</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>470.84</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>175.56</v>
+        <v>192.57</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
       <c r="X27" s="11" t="n"/>
       <c r="Y27" s="12" t="inlineStr">
         <is>
-          <t>Comissão apurada R$ 235,42 × 2. 40 horas extras.</t>
+          <t>Comissão apurada R$ 235,42 × 2. Horas extras corrigidas: 16 h a 50% (R$ 176,84) + 24 h a 100% (R$ 353,67). O holerite da Betel saiu com 40 h a 50% — pedir para refazer (sobem HE, DSR e INSS).</t>
         </is>
       </c>
     </row>
@@ -2817,93 +2817,100 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>• DSR EM DUPLICIDADE: a rubrica 420 (Repouso Remunerado) já foi calculada sobre comissão + horas extras, e a Betel ainda lançou a rubrica 057 (DSR/hora extra). São R$ 51,01 do EDEY, R$ 46,51 da NATI, R$ 10,38 de VALÉRIA, SARA e CAMILA e R$ 85,02 do INIURLE — R$ 213,68 no total. Confirmar com a contabilidade.</t>
+          <t>• INIURLE (Trancoso): horas extras corrigidas para 16 h a 50% + 24 h a 100% (R$ 530,51, eram R$ 442,09). A diferença de R$ 105,43 é antes do novo INSS — a Betel precisa refazer o holerite.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>• Prêmio cota geral e prêmio pré-vencidos, conforme a apuração de metas de cada loja.</t>
+          <t>• DSR EM DUPLICIDADE: a rubrica 420 (Repouso Remunerado) já foi calculada sobre comissão + horas extras, e a Betel ainda lançou a rubrica 057 (DSR/hora extra). São R$ 51,01 do EDEY, R$ 46,51 da NATI, R$ 10,38 de VALÉRIA, SARA e CAMILA e R$ 85,02 do INIURLE — R$ 213,68 no total. Confirmar com a contabilidade.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>• A coluna FÉRIAS PAGAS À PARTE é só lembrete para o contas a pagar: recibo de férias pago fora do holerite, NÃO entra no líquido. Em agosto: JOEL (Arraial, férias de 01 a 31/08) e GENECIR (Centro, férias de 01 a 30/08).</t>
+          <t>• Prêmio cota geral e prêmio pré-vencidos, conforme a apuração de metas de cada loja.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
+          <t>• A coluna FÉRIAS PAGAS À PARTE é só lembrete para o contas a pagar: recibo de férias pago fora do holerite, NÃO entra no líquido. Em agosto: JOEL (Arraial, férias de 01 a 31/08) e GENECIR (Centro, férias de 01 a 30/08).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
           <t>• Diárias dos folguistas SERGIO (R$ 150,00) e ANA CELIA (R$ 100,00), na loja Centro — vão para o contas a pagar, fora do holerite.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>CRITÉRIOS USADOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
+          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
+          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
+          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>• Os incentivos são adiantados em dinheiro durante o mês e NÃO aparecem no holerite da Betel; aqui entram como provento e como desconto, sem afetar o líquido.</t>
+          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>• Prêmios, vales, vale-transporte, INSS e IRRF foram lidos do holerite de agosto/2026 emitido pela Betel Contabilidade.</t>
+          <t>• Os incentivos são adiantados em dinheiro durante o mês e NÃO aparecem no holerite da Betel; aqui entram como provento e como desconto, sem afetar o líquido.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
+          <t>• Prêmios, vales, vale-transporte, INSS e IRRF foram lidos do holerite de agosto/2026 emitido pela Betel Contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
           <t>• Comissões e incentivos vêm do relatório do InovaFarma de 01/08 a 31/08/2026, extraído em 03/09/2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Y29"/>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="A33:Y33"/>
     <mergeCell ref="A47:Y47"/>
@@ -2923,6 +2930,7 @@
     <mergeCell ref="A41:Y41"/>
     <mergeCell ref="A46:Y46"/>
     <mergeCell ref="A37:Y37"/>
+    <mergeCell ref="A50:Y50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -2036,7 +2036,7 @@
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="12" t="inlineStr">
         <is>
-          <t>NÃO CONSTA no holerite de agosto emitido pela Betel para esta loja — verificar em qual empresa foi lançado.</t>
+          <t>Registrado na matriz, mas o holerite de agosto dele NÃO veio no arquivo da Betel — pedir o holerite (R$ 1.621,00).</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>• PEDRO (Centro): não consta no holerite emitido pela Betel para esta loja.</t>
+          <t>• PEDRO (Centro): registrado na matriz, mas o holerite de agosto dele não veio no arquivo da Betel — pedir o holerite (R$ 1.621,00).</t>
         </is>
       </c>
     </row>
